--- a/public/plantilla-mensual-sst.xlsx
+++ b/public/plantilla-mensual-sst.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="40">
+  <numFmts count="0"/>
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -301,6 +302,15 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1029,7 +1039,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1945,6 +1955,58 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2665,16 +2727,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="364" t="n"/>
+      <c r="D11" s="365" t="n"/>
+      <c r="E11" s="365" t="n"/>
+      <c r="F11" s="365" t="n"/>
+      <c r="G11" s="365" t="n"/>
+      <c r="H11" s="365" t="n"/>
+      <c r="I11" s="365" t="n"/>
+      <c r="J11" s="365" t="n"/>
+      <c r="K11" s="365" t="n"/>
+      <c r="L11" s="366" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2683,20 +2745,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="364" t="n"/>
+      <c r="D12" s="365" t="n"/>
+      <c r="E12" s="365" t="n"/>
+      <c r="F12" s="365" t="n"/>
+      <c r="G12" s="366" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="364" t="n"/>
+      <c r="K12" s="365" t="n"/>
+      <c r="L12" s="366" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2705,24 +2767,24 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="69" t="n"/>
-      <c r="D13" s="89" t="n"/>
+      <c r="C13" s="367" t="n"/>
+      <c r="D13" s="366" t="n"/>
       <c r="E13" s="59" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
       <c r="F13" s="89" t="n"/>
-      <c r="G13" s="69" t="n"/>
-      <c r="H13" s="89" t="n"/>
+      <c r="G13" s="367" t="n"/>
+      <c r="H13" s="366" t="n"/>
       <c r="I13" s="59" t="inlineStr">
         <is>
           <t>Informe N°</t>
         </is>
       </c>
       <c r="J13" s="89" t="n"/>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="K13" s="367" t="n"/>
+      <c r="L13" s="366" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2731,24 +2793,24 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="69" t="n"/>
-      <c r="D14" s="89" t="n"/>
+      <c r="C14" s="367" t="n"/>
+      <c r="D14" s="366" t="n"/>
       <c r="E14" s="59" t="inlineStr">
         <is>
           <t>Horas-hombre (HHT)</t>
         </is>
       </c>
       <c r="F14" s="89" t="n"/>
-      <c r="G14" s="69" t="n"/>
-      <c r="H14" s="89" t="n"/>
+      <c r="G14" s="367" t="n"/>
+      <c r="H14" s="366" t="n"/>
       <c r="I14" s="59" t="inlineStr">
         <is>
           <t>Días trabajados</t>
         </is>
       </c>
       <c r="J14" s="89" t="n"/>
-      <c r="K14" s="69" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="K14" s="367" t="n"/>
+      <c r="L14" s="366" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="127">
       <c r="A15" s="137" t="inlineStr">
@@ -2807,10 +2869,10 @@
       <c r="L16" s="348" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="127">
-      <c r="A17" s="306" t="n">
+      <c r="A17" s="368" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="230" t="inlineStr">
+      <c r="B17" s="369" t="inlineStr">
         <is>
           <t>Frecuencia de accidentalidad (%)</t>
         </is>
@@ -2818,22 +2880,22 @@
       <c r="C17" s="98" t="n"/>
       <c r="D17" s="98" t="n"/>
       <c r="E17" s="97" t="n"/>
-      <c r="F17" s="361" t="n"/>
-      <c r="G17" s="97" t="n"/>
-      <c r="H17" s="361" t="n"/>
-      <c r="I17" s="97" t="n"/>
-      <c r="J17" s="361" t="n"/>
-      <c r="K17" s="362">
+      <c r="F17" s="370" t="n"/>
+      <c r="G17" s="371" t="n"/>
+      <c r="H17" s="372" t="n"/>
+      <c r="I17" s="371" t="n"/>
+      <c r="J17" s="372" t="n"/>
+      <c r="K17" s="373">
         <f>IF(OR(F17="",J17=""),"",IF(F17&lt;=J17,"Cumple","No cumple"))</f>
         <v/>
       </c>
       <c r="L17" s="97" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="127">
-      <c r="A18" s="306" t="n">
+      <c r="A18" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="230" t="inlineStr">
+      <c r="B18" s="369" t="inlineStr">
         <is>
           <t>Severidad de accidentalidad (%)</t>
         </is>
@@ -2841,22 +2903,22 @@
       <c r="C18" s="98" t="n"/>
       <c r="D18" s="98" t="n"/>
       <c r="E18" s="97" t="n"/>
-      <c r="F18" s="361" t="n"/>
-      <c r="G18" s="97" t="n"/>
-      <c r="H18" s="361" t="n"/>
-      <c r="I18" s="97" t="n"/>
-      <c r="J18" s="361" t="n"/>
-      <c r="K18" s="362">
+      <c r="F18" s="370" t="n"/>
+      <c r="G18" s="371" t="n"/>
+      <c r="H18" s="372" t="n"/>
+      <c r="I18" s="371" t="n"/>
+      <c r="J18" s="372" t="n"/>
+      <c r="K18" s="373">
         <f>IF(OR(F18="",J18=""),"",IF(F18&lt;=J18,"Cumple","No cumple"))</f>
         <v/>
       </c>
       <c r="L18" s="97" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="369" t="inlineStr">
         <is>
           <t>Proporción de AT mortales (%)</t>
         </is>
@@ -2864,22 +2926,22 @@
       <c r="C19" s="98" t="n"/>
       <c r="D19" s="98" t="n"/>
       <c r="E19" s="97" t="n"/>
-      <c r="F19" s="361" t="n"/>
-      <c r="G19" s="97" t="n"/>
-      <c r="H19" s="361" t="n"/>
-      <c r="I19" s="97" t="n"/>
-      <c r="J19" s="361" t="n"/>
-      <c r="K19" s="362">
+      <c r="F19" s="370" t="n"/>
+      <c r="G19" s="371" t="n"/>
+      <c r="H19" s="372" t="n"/>
+      <c r="I19" s="371" t="n"/>
+      <c r="J19" s="372" t="n"/>
+      <c r="K19" s="373">
         <f>IF(OR(F19="",J19=""),"",IF(F19&lt;=J19,"Cumple","No cumple"))</f>
         <v/>
       </c>
       <c r="L19" s="97" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="230" t="inlineStr">
+      <c r="B20" s="369" t="inlineStr">
         <is>
           <t>Índice de frecuencia (IF)</t>
         </is>
@@ -2887,22 +2949,22 @@
       <c r="C20" s="98" t="n"/>
       <c r="D20" s="98" t="n"/>
       <c r="E20" s="97" t="n"/>
-      <c r="F20" s="361" t="n"/>
-      <c r="G20" s="97" t="n"/>
-      <c r="H20" s="361" t="n"/>
-      <c r="I20" s="97" t="n"/>
-      <c r="J20" s="361" t="n"/>
-      <c r="K20" s="362">
+      <c r="F20" s="370" t="n"/>
+      <c r="G20" s="371" t="n"/>
+      <c r="H20" s="372" t="n"/>
+      <c r="I20" s="371" t="n"/>
+      <c r="J20" s="372" t="n"/>
+      <c r="K20" s="373">
         <f>IF(OR(F20="",J20=""),"",IF(F20&lt;=J20,"Cumple","No cumple"))</f>
         <v/>
       </c>
       <c r="L20" s="97" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="368" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="230" t="inlineStr">
+      <c r="B21" s="369" t="inlineStr">
         <is>
           <t>Índice de severidad (IS)</t>
         </is>
@@ -2910,22 +2972,22 @@
       <c r="C21" s="98" t="n"/>
       <c r="D21" s="98" t="n"/>
       <c r="E21" s="97" t="n"/>
-      <c r="F21" s="361" t="n"/>
-      <c r="G21" s="97" t="n"/>
-      <c r="H21" s="361" t="n"/>
-      <c r="I21" s="97" t="n"/>
-      <c r="J21" s="361" t="n"/>
-      <c r="K21" s="362">
+      <c r="F21" s="370" t="n"/>
+      <c r="G21" s="371" t="n"/>
+      <c r="H21" s="372" t="n"/>
+      <c r="I21" s="371" t="n"/>
+      <c r="J21" s="372" t="n"/>
+      <c r="K21" s="373">
         <f>IF(OR(F21="",J21=""),"",IF(F21&lt;=J21,"Cumple","No cumple"))</f>
         <v/>
       </c>
       <c r="L21" s="97" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="368" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="230" t="inlineStr">
+      <c r="B22" s="369" t="inlineStr">
         <is>
           <t>Índice de lesiones incapacitantes (ILI)</t>
         </is>
@@ -2933,22 +2995,22 @@
       <c r="C22" s="98" t="n"/>
       <c r="D22" s="98" t="n"/>
       <c r="E22" s="97" t="n"/>
-      <c r="F22" s="361" t="n"/>
-      <c r="G22" s="97" t="n"/>
-      <c r="H22" s="361" t="n"/>
-      <c r="I22" s="97" t="n"/>
-      <c r="J22" s="361" t="n"/>
-      <c r="K22" s="362">
+      <c r="F22" s="370" t="n"/>
+      <c r="G22" s="371" t="n"/>
+      <c r="H22" s="372" t="n"/>
+      <c r="I22" s="371" t="n"/>
+      <c r="J22" s="372" t="n"/>
+      <c r="K22" s="373">
         <f>IF(OR(F22="",J22=""),"",IF(F22&lt;=J22,"Cumple","No cumple"))</f>
         <v/>
       </c>
       <c r="L22" s="97" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="368" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="369" t="inlineStr">
         <is>
           <t>Ausentismo por causa médica (%)</t>
         </is>
@@ -2956,12 +3018,12 @@
       <c r="C23" s="98" t="n"/>
       <c r="D23" s="98" t="n"/>
       <c r="E23" s="97" t="n"/>
-      <c r="F23" s="361" t="n"/>
-      <c r="G23" s="97" t="n"/>
-      <c r="H23" s="361" t="n"/>
-      <c r="I23" s="97" t="n"/>
-      <c r="J23" s="361" t="n"/>
-      <c r="K23" s="362">
+      <c r="F23" s="370" t="n"/>
+      <c r="G23" s="371" t="n"/>
+      <c r="H23" s="372" t="n"/>
+      <c r="I23" s="371" t="n"/>
+      <c r="J23" s="372" t="n"/>
+      <c r="K23" s="373">
         <f>IF(OR(F23="",J23=""),"",IF(F23&lt;=J23,"Cumple","No cumple"))</f>
         <v/>
       </c>
@@ -3024,10 +3086,10 @@
       <c r="L25" s="348" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="368" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="230" t="inlineStr">
+      <c r="B26" s="369" t="inlineStr">
         <is>
           <t>Capacitaciones y entrenamientos</t>
         </is>
@@ -3036,21 +3098,21 @@
       <c r="D26" s="98" t="n"/>
       <c r="E26" s="98" t="n"/>
       <c r="F26" s="97" t="n"/>
-      <c r="G26" s="306" t="n"/>
-      <c r="H26" s="306" t="n"/>
-      <c r="I26" s="360">
+      <c r="G26" s="374" t="n"/>
+      <c r="H26" s="374" t="n"/>
+      <c r="I26" s="375">
         <f>IF(OR(G26="",G26=0,H26=""),"",H26/G26)</f>
         <v/>
       </c>
-      <c r="J26" s="230" t="n"/>
-      <c r="K26" s="98" t="n"/>
-      <c r="L26" s="97" t="n"/>
+      <c r="J26" s="376" t="n"/>
+      <c r="K26" s="377" t="n"/>
+      <c r="L26" s="371" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="127">
-      <c r="A27" s="306" t="n">
+      <c r="A27" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="230" t="inlineStr">
+      <c r="B27" s="369" t="inlineStr">
         <is>
           <t>Inspecciones de seguridad</t>
         </is>
@@ -3059,21 +3121,21 @@
       <c r="D27" s="98" t="n"/>
       <c r="E27" s="98" t="n"/>
       <c r="F27" s="97" t="n"/>
-      <c r="G27" s="306" t="n"/>
-      <c r="H27" s="306" t="n"/>
-      <c r="I27" s="360">
+      <c r="G27" s="374" t="n"/>
+      <c r="H27" s="374" t="n"/>
+      <c r="I27" s="375">
         <f>IF(OR(G27="",G27=0,H27=""),"",H27/G27)</f>
         <v/>
       </c>
-      <c r="J27" s="230" t="n"/>
-      <c r="K27" s="98" t="n"/>
-      <c r="L27" s="97" t="n"/>
+      <c r="J27" s="376" t="n"/>
+      <c r="K27" s="377" t="n"/>
+      <c r="L27" s="371" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="127">
-      <c r="A28" s="306" t="n">
+      <c r="A28" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="230" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <t>Charlas diarias de seguridad</t>
         </is>
@@ -3082,21 +3144,21 @@
       <c r="D28" s="98" t="n"/>
       <c r="E28" s="98" t="n"/>
       <c r="F28" s="97" t="n"/>
-      <c r="G28" s="306" t="n"/>
-      <c r="H28" s="306" t="n"/>
-      <c r="I28" s="360">
+      <c r="G28" s="374" t="n"/>
+      <c r="H28" s="374" t="n"/>
+      <c r="I28" s="375">
         <f>IF(OR(G28="",G28=0,H28=""),"",H28/G28)</f>
         <v/>
       </c>
-      <c r="J28" s="230" t="n"/>
-      <c r="K28" s="98" t="n"/>
-      <c r="L28" s="97" t="n"/>
+      <c r="J28" s="376" t="n"/>
+      <c r="K28" s="377" t="n"/>
+      <c r="L28" s="371" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="127">
-      <c r="A29" s="306" t="n">
+      <c r="A29" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="230" t="inlineStr">
+      <c r="B29" s="369" t="inlineStr">
         <is>
           <t>Inducciones SST</t>
         </is>
@@ -3105,21 +3167,21 @@
       <c r="D29" s="98" t="n"/>
       <c r="E29" s="98" t="n"/>
       <c r="F29" s="97" t="n"/>
-      <c r="G29" s="306" t="n"/>
-      <c r="H29" s="306" t="n"/>
-      <c r="I29" s="360">
+      <c r="G29" s="374" t="n"/>
+      <c r="H29" s="374" t="n"/>
+      <c r="I29" s="375">
         <f>IF(OR(G29="",G29=0,H29=""),"",H29/G29)</f>
         <v/>
       </c>
-      <c r="J29" s="230" t="n"/>
-      <c r="K29" s="98" t="n"/>
-      <c r="L29" s="97" t="n"/>
+      <c r="J29" s="376" t="n"/>
+      <c r="K29" s="377" t="n"/>
+      <c r="L29" s="371" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="127">
-      <c r="A30" s="306" t="n">
+      <c r="A30" s="368" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="230" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <t>Permisos de trabajo de alto riesgo</t>
         </is>
@@ -3128,21 +3190,21 @@
       <c r="D30" s="98" t="n"/>
       <c r="E30" s="98" t="n"/>
       <c r="F30" s="97" t="n"/>
-      <c r="G30" s="306" t="n"/>
-      <c r="H30" s="306" t="n"/>
-      <c r="I30" s="360">
+      <c r="G30" s="374" t="n"/>
+      <c r="H30" s="374" t="n"/>
+      <c r="I30" s="375">
         <f>IF(OR(G30="",G30=0,H30=""),"",H30/G30)</f>
         <v/>
       </c>
-      <c r="J30" s="230" t="n"/>
-      <c r="K30" s="98" t="n"/>
-      <c r="L30" s="97" t="n"/>
+      <c r="J30" s="376" t="n"/>
+      <c r="K30" s="377" t="n"/>
+      <c r="L30" s="371" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="127">
-      <c r="A31" s="306" t="n">
+      <c r="A31" s="368" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="230" t="inlineStr">
+      <c r="B31" s="369" t="inlineStr">
         <is>
           <t>Análisis de trabajo seguro (ATS)</t>
         </is>
@@ -3151,21 +3213,21 @@
       <c r="D31" s="98" t="n"/>
       <c r="E31" s="98" t="n"/>
       <c r="F31" s="97" t="n"/>
-      <c r="G31" s="306" t="n"/>
-      <c r="H31" s="306" t="n"/>
-      <c r="I31" s="360">
+      <c r="G31" s="374" t="n"/>
+      <c r="H31" s="374" t="n"/>
+      <c r="I31" s="375">
         <f>IF(OR(G31="",G31=0,H31=""),"",H31/G31)</f>
         <v/>
       </c>
-      <c r="J31" s="230" t="n"/>
-      <c r="K31" s="98" t="n"/>
-      <c r="L31" s="97" t="n"/>
+      <c r="J31" s="376" t="n"/>
+      <c r="K31" s="377" t="n"/>
+      <c r="L31" s="371" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="127">
-      <c r="A32" s="306" t="n">
+      <c r="A32" s="368" t="n">
         <v>7</v>
       </c>
-      <c r="B32" s="230" t="inlineStr">
+      <c r="B32" s="369" t="inlineStr">
         <is>
           <t>Actos y condiciones inseguras reportados</t>
         </is>
@@ -3174,21 +3236,21 @@
       <c r="D32" s="98" t="n"/>
       <c r="E32" s="98" t="n"/>
       <c r="F32" s="97" t="n"/>
-      <c r="G32" s="306" t="n"/>
-      <c r="H32" s="306" t="n"/>
-      <c r="I32" s="360">
+      <c r="G32" s="374" t="n"/>
+      <c r="H32" s="374" t="n"/>
+      <c r="I32" s="375">
         <f>IF(OR(G32="",G32=0,H32=""),"",H32/G32)</f>
         <v/>
       </c>
-      <c r="J32" s="230" t="n"/>
-      <c r="K32" s="98" t="n"/>
-      <c r="L32" s="97" t="n"/>
+      <c r="J32" s="376" t="n"/>
+      <c r="K32" s="377" t="n"/>
+      <c r="L32" s="371" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="127">
-      <c r="A33" s="306" t="n">
+      <c r="A33" s="368" t="n">
         <v>8</v>
       </c>
-      <c r="B33" s="230" t="inlineStr">
+      <c r="B33" s="369" t="inlineStr">
         <is>
           <t>Acciones correctivas cerradas</t>
         </is>
@@ -3197,15 +3259,15 @@
       <c r="D33" s="98" t="n"/>
       <c r="E33" s="98" t="n"/>
       <c r="F33" s="97" t="n"/>
-      <c r="G33" s="306" t="n"/>
-      <c r="H33" s="306" t="n"/>
-      <c r="I33" s="360">
+      <c r="G33" s="374" t="n"/>
+      <c r="H33" s="374" t="n"/>
+      <c r="I33" s="375">
         <f>IF(OR(G33="",G33=0,H33=""),"",H33/G33)</f>
         <v/>
       </c>
-      <c r="J33" s="230" t="n"/>
-      <c r="K33" s="98" t="n"/>
-      <c r="L33" s="97" t="n"/>
+      <c r="J33" s="376" t="n"/>
+      <c r="K33" s="377" t="n"/>
+      <c r="L33" s="371" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="127">
       <c r="A34" s="137" t="inlineStr">
@@ -3264,18 +3326,18 @@
       <c r="L35" s="348" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1" s="127">
-      <c r="A36" s="69" t="n"/>
-      <c r="B36" s="89" t="n"/>
-      <c r="C36" s="69" t="n"/>
-      <c r="D36" s="89" t="n"/>
-      <c r="E36" s="69" t="n"/>
-      <c r="F36" s="89" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="89" t="n"/>
-      <c r="I36" s="69" t="n"/>
-      <c r="J36" s="89" t="n"/>
-      <c r="K36" s="69" t="n"/>
-      <c r="L36" s="89" t="n"/>
+      <c r="A36" s="367" t="n"/>
+      <c r="B36" s="366" t="n"/>
+      <c r="C36" s="367" t="n"/>
+      <c r="D36" s="366" t="n"/>
+      <c r="E36" s="367" t="n"/>
+      <c r="F36" s="366" t="n"/>
+      <c r="G36" s="367" t="n"/>
+      <c r="H36" s="366" t="n"/>
+      <c r="I36" s="367" t="n"/>
+      <c r="J36" s="366" t="n"/>
+      <c r="K36" s="367" t="n"/>
+      <c r="L36" s="366" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="127">
       <c r="A37" s="137" t="inlineStr">
@@ -3302,16 +3364,16 @@
         </is>
       </c>
       <c r="B38" s="89" t="n"/>
-      <c r="C38" s="100" t="n"/>
-      <c r="D38" s="93" t="n"/>
-      <c r="E38" s="93" t="n"/>
-      <c r="F38" s="93" t="n"/>
-      <c r="G38" s="93" t="n"/>
-      <c r="H38" s="93" t="n"/>
-      <c r="I38" s="93" t="n"/>
-      <c r="J38" s="93" t="n"/>
-      <c r="K38" s="93" t="n"/>
-      <c r="L38" s="89" t="n"/>
+      <c r="C38" s="378" t="n"/>
+      <c r="D38" s="365" t="n"/>
+      <c r="E38" s="365" t="n"/>
+      <c r="F38" s="365" t="n"/>
+      <c r="G38" s="365" t="n"/>
+      <c r="H38" s="365" t="n"/>
+      <c r="I38" s="365" t="n"/>
+      <c r="J38" s="365" t="n"/>
+      <c r="K38" s="365" t="n"/>
+      <c r="L38" s="366" t="n"/>
     </row>
     <row r="39" ht="44" customHeight="1" s="127">
       <c r="A39" s="59" t="inlineStr">
@@ -3320,16 +3382,16 @@
         </is>
       </c>
       <c r="B39" s="89" t="n"/>
-      <c r="C39" s="100" t="n"/>
-      <c r="D39" s="93" t="n"/>
-      <c r="E39" s="93" t="n"/>
-      <c r="F39" s="93" t="n"/>
-      <c r="G39" s="93" t="n"/>
-      <c r="H39" s="93" t="n"/>
-      <c r="I39" s="93" t="n"/>
-      <c r="J39" s="93" t="n"/>
-      <c r="K39" s="93" t="n"/>
-      <c r="L39" s="89" t="n"/>
+      <c r="C39" s="378" t="n"/>
+      <c r="D39" s="365" t="n"/>
+      <c r="E39" s="365" t="n"/>
+      <c r="F39" s="365" t="n"/>
+      <c r="G39" s="365" t="n"/>
+      <c r="H39" s="365" t="n"/>
+      <c r="I39" s="365" t="n"/>
+      <c r="J39" s="365" t="n"/>
+      <c r="K39" s="365" t="n"/>
+      <c r="L39" s="366" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="127">
       <c r="A40" s="137" t="inlineStr">
@@ -3356,16 +3418,16 @@
         </is>
       </c>
       <c r="B41" s="89" t="n"/>
-      <c r="C41" s="100" t="n"/>
-      <c r="D41" s="93" t="n"/>
-      <c r="E41" s="93" t="n"/>
-      <c r="F41" s="93" t="n"/>
-      <c r="G41" s="93" t="n"/>
-      <c r="H41" s="93" t="n"/>
-      <c r="I41" s="93" t="n"/>
-      <c r="J41" s="93" t="n"/>
-      <c r="K41" s="93" t="n"/>
-      <c r="L41" s="89" t="n"/>
+      <c r="C41" s="378" t="n"/>
+      <c r="D41" s="365" t="n"/>
+      <c r="E41" s="365" t="n"/>
+      <c r="F41" s="365" t="n"/>
+      <c r="G41" s="365" t="n"/>
+      <c r="H41" s="365" t="n"/>
+      <c r="I41" s="365" t="n"/>
+      <c r="J41" s="365" t="n"/>
+      <c r="K41" s="365" t="n"/>
+      <c r="L41" s="366" t="n"/>
     </row>
     <row r="42" ht="50" customHeight="1" s="127">
       <c r="A42" s="59" t="inlineStr">
@@ -3374,16 +3436,16 @@
         </is>
       </c>
       <c r="B42" s="89" t="n"/>
-      <c r="C42" s="100" t="n"/>
-      <c r="D42" s="93" t="n"/>
-      <c r="E42" s="93" t="n"/>
-      <c r="F42" s="93" t="n"/>
-      <c r="G42" s="93" t="n"/>
-      <c r="H42" s="93" t="n"/>
-      <c r="I42" s="93" t="n"/>
-      <c r="J42" s="93" t="n"/>
-      <c r="K42" s="93" t="n"/>
-      <c r="L42" s="89" t="n"/>
+      <c r="C42" s="378" t="n"/>
+      <c r="D42" s="365" t="n"/>
+      <c r="E42" s="365" t="n"/>
+      <c r="F42" s="365" t="n"/>
+      <c r="G42" s="365" t="n"/>
+      <c r="H42" s="365" t="n"/>
+      <c r="I42" s="365" t="n"/>
+      <c r="J42" s="365" t="n"/>
+      <c r="K42" s="365" t="n"/>
+      <c r="L42" s="366" t="n"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="127">
       <c r="A43" s="137" t="inlineStr">
@@ -3436,24 +3498,24 @@
         </is>
       </c>
       <c r="B45" s="97" t="n"/>
-      <c r="C45" s="301" t="n"/>
-      <c r="D45" s="97" t="n"/>
+      <c r="C45" s="376" t="n"/>
+      <c r="D45" s="371" t="n"/>
       <c r="E45" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F45" s="97" t="n"/>
-      <c r="G45" s="301" t="n"/>
-      <c r="H45" s="97" t="n"/>
+      <c r="G45" s="376" t="n"/>
+      <c r="H45" s="371" t="n"/>
       <c r="I45" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J45" s="97" t="n"/>
-      <c r="K45" s="301" t="n"/>
-      <c r="L45" s="97" t="n"/>
+      <c r="K45" s="376" t="n"/>
+      <c r="L45" s="371" t="n"/>
     </row>
     <row r="46" ht="21" customHeight="1" s="127">
       <c r="A46" s="302" t="inlineStr">
@@ -3462,24 +3524,24 @@
         </is>
       </c>
       <c r="B46" s="97" t="n"/>
-      <c r="C46" s="301" t="n"/>
-      <c r="D46" s="97" t="n"/>
+      <c r="C46" s="376" t="n"/>
+      <c r="D46" s="371" t="n"/>
       <c r="E46" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F46" s="97" t="n"/>
-      <c r="G46" s="301" t="n"/>
-      <c r="H46" s="97" t="n"/>
+      <c r="G46" s="376" t="n"/>
+      <c r="H46" s="371" t="n"/>
       <c r="I46" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J46" s="97" t="n"/>
-      <c r="K46" s="301" t="n"/>
-      <c r="L46" s="97" t="n"/>
+      <c r="K46" s="376" t="n"/>
+      <c r="L46" s="371" t="n"/>
     </row>
     <row r="47" ht="21" customHeight="1" s="127">
       <c r="A47" s="302" t="inlineStr">
@@ -3488,24 +3550,24 @@
         </is>
       </c>
       <c r="B47" s="97" t="n"/>
-      <c r="C47" s="301" t="n"/>
-      <c r="D47" s="97" t="n"/>
+      <c r="C47" s="376" t="n"/>
+      <c r="D47" s="371" t="n"/>
       <c r="E47" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F47" s="97" t="n"/>
-      <c r="G47" s="301" t="n"/>
-      <c r="H47" s="97" t="n"/>
+      <c r="G47" s="376" t="n"/>
+      <c r="H47" s="371" t="n"/>
       <c r="I47" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J47" s="97" t="n"/>
-      <c r="K47" s="301" t="n"/>
-      <c r="L47" s="97" t="n"/>
+      <c r="K47" s="376" t="n"/>
+      <c r="L47" s="371" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
@@ -3519,6 +3581,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="127">
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="B25:F25"/>
